--- a/Dashboard/TRENDKART/TRENDKARD DASHBOARD.xlsx
+++ b/Dashboard/TRENDKART/TRENDKARD DASHBOARD.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5eb3c2e9862f82c0/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Subha\02_Excel\Project\Dashboard\TRENDKART\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E317019D-8474-437E-B632-FA2964028239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8C619C-3D3D-4B1E-A650-D0BECF5D31E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{953235A4-3870-4C6C-8713-8653B156B69C}"/>
   </bookViews>
@@ -336,10 +336,14 @@
   </cellStyleXfs>
   <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -347,10 +351,71 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -359,10 +424,22 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -371,89 +448,12 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -525,9 +525,9 @@
             </c:marker>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:ln w="28575" cap="rnd">
+              <a:ln w="31750" cap="rnd">
                 <a:solidFill>
-                  <a:schemeClr val="accent1"/>
+                  <a:schemeClr val="accent6"/>
                 </a:solidFill>
                 <a:round/>
               </a:ln>
@@ -546,9 +546,9 @@
             </c:marker>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:ln w="28575" cap="rnd">
+              <a:ln w="31750" cap="rnd">
                 <a:solidFill>
-                  <a:schemeClr val="accent2"/>
+                  <a:schemeClr val="accent5"/>
                 </a:solidFill>
                 <a:round/>
               </a:ln>
@@ -567,9 +567,9 @@
             </c:marker>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:ln w="28575" cap="rnd">
+              <a:ln w="31750" cap="rnd">
                 <a:solidFill>
-                  <a:schemeClr val="accent3"/>
+                  <a:schemeClr val="accent4"/>
                 </a:solidFill>
                 <a:round/>
               </a:ln>
@@ -588,9 +588,11 @@
             </c:marker>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:ln w="28575" cap="rnd">
+              <a:ln w="31750" cap="rnd">
                 <a:solidFill>
-                  <a:schemeClr val="accent4"/>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:round/>
               </a:ln>
@@ -609,9 +611,11 @@
             </c:marker>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:ln w="28575" cap="rnd">
+              <a:ln w="31750" cap="rnd">
                 <a:solidFill>
-                  <a:schemeClr val="accent5"/>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:round/>
               </a:ln>
@@ -630,9 +634,11 @@
             </c:marker>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:ln w="28575" cap="rnd">
+              <a:ln w="31750" cap="rnd">
                 <a:solidFill>
-                  <a:schemeClr val="accent6"/>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:round/>
               </a:ln>
@@ -651,10 +657,11 @@
             </c:marker>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:ln w="28575" cap="rnd">
+              <a:ln w="31750" cap="rnd">
                 <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="60000"/>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:round/>
@@ -674,10 +681,11 @@
             </c:marker>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:ln w="28575" cap="rnd">
+              <a:ln w="31750" cap="rnd">
                 <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="60000"/>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:round/>
@@ -697,10 +705,11 @@
             </c:marker>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:ln w="28575" cap="rnd">
+              <a:ln w="31750" cap="rnd">
                 <a:solidFill>
-                  <a:schemeClr val="accent3">
-                    <a:lumMod val="60000"/>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:round/>
@@ -720,10 +729,10 @@
             </c:marker>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:ln w="28575" cap="rnd">
+              <a:ln w="31750" cap="rnd">
                 <a:solidFill>
-                  <a:schemeClr val="accent4">
-                    <a:lumMod val="60000"/>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="80000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:round/>
@@ -743,10 +752,10 @@
             </c:marker>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:ln w="28575" cap="rnd">
+              <a:ln w="31750" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent5">
-                    <a:lumMod val="60000"/>
+                    <a:lumMod val="80000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:round/>
@@ -766,10 +775,10 @@
             </c:marker>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:ln w="28575" cap="rnd">
+              <a:ln w="31750" cap="rnd">
                 <a:solidFill>
-                  <a:schemeClr val="accent6">
-                    <a:lumMod val="60000"/>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="80000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:round/>
@@ -782,11 +791,26 @@
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="movingAvg"/>
+            <c:period val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:numRef>
               <c:f>[1]Calc!$M$2:$M$13</c:f>
               <c:numCache>
-                <c:formatCode>mmm\-yy</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>45383</c:v>
@@ -891,23 +915,54 @@
         <c:axId val="10"/>
         <c:axId val="100"/>
       </c:lineChart>
-      <c:dateAx>
+      <c:catAx>
         <c:axId val="10"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="mmm\-yy" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="100"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:baseTimeUnit val="months"/>
-      </c:dateAx>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
       <c:valAx>
         <c:axId val="100"/>
         <c:scaling>
@@ -919,7 +974,7 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
+                <a:schemeClr val="tx2">
                   <a:lumMod val="15000"/>
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
@@ -929,61 +984,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-IN"/>
-                  <a:t>Sales Amount (₹)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="1"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1002,10 +1002,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx2"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1041,13 +1038,10 @@
         <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr rtl="0">
+          <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx2"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -1068,7 +1062,7 @@
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
+        <a:schemeClr val="tx2">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -1116,7 +1110,7 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="7.8929227279548542E-2"/>
+          <c:x val="0.10358235856932752"/>
           <c:y val="0"/>
           <c:w val="0.75179564762725193"/>
           <c:h val="0.99431003584229394"/>
@@ -1144,7 +1138,82 @@
             </a:ln>
           </c:spPr>
           <c:dLbls>
-            <c:delete val="1"/>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="8.4322041748365967E-2"/>
+                      <c:h val="0.10418270602903783"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-0683-4E85-9DDD-5AC1B41DCFCD}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="9.5706655845805094E-2"/>
+                      <c:h val="0.10418270602903783"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-0683-4E85-9DDD-5AC1B41DCFCD}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-0683-4E85-9DDD-5AC1B41DCFCD}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-0683-4E85-9DDD-5AC1B41DCFCD}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -1224,12 +1293,12 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:showLegendKey val="1"/>
+          <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
-          <c:showCatName val="1"/>
-          <c:showSerName val="1"/>
-          <c:showPercent val="1"/>
-          <c:showBubbleSize val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
           <c:showLeaderLines val="1"/>
         </c:dLbls>
         <c:firstSliceAng val="0"/>
@@ -1278,7 +1347,17 @@
   <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="4.583333333333333E-2"/>
+          <c:y val="9.3217061375897373E-2"/>
+          <c:w val="0.90833333333333333"/>
+          <c:h val="0.84224804997925062"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -1298,11 +1377,45 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="F79646">
+                <a:alpha val="50196"/>
+              </a:srgbClr>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                <a:schemeClr val="accent6">
+                  <a:alpha val="40000"/>
+                </a:schemeClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:invertIfNegative val="1"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>[1]Calc!$S$2:$S$3</c:f>
@@ -1333,14 +1446,34 @@
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFC000"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                  <a:effectLst>
+                    <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                      <a:schemeClr val="accent6">
+                        <a:alpha val="40000"/>
+                      </a:schemeClr>
+                    </a:outerShdw>
+                  </a:effectLst>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-F10D-4359-8AD6-5BF5D991F209}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -1355,28 +1488,13 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-IN"/>
-                  <a:t>Sales Channel</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="1"/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="100"/>
@@ -1391,29 +1509,11 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-IN"/>
-                  <a:t>Sales Amount (₹)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="1"/>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="10"/>
@@ -1421,6 +1521,10 @@
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="1"/>
@@ -2694,13 +2798,10 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
   <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
   <cs:variation/>
   <cs:variation>
     <a:lumMod val="60000"/>
@@ -2814,33 +2915,27 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="231">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -2855,7 +2950,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -2863,7 +2958,7 @@
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -2871,17 +2966,14 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:dataLabel>
@@ -2890,9 +2982,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
@@ -2915,45 +3006,35 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="2"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="2"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="31750" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -2962,36 +3043,32 @@
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="2"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="12700">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt2"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -3007,21 +3084,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -3055,17 +3127,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -3074,14 +3146,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3093,26 +3164,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -3126,17 +3191,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln>
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="5000"/>
             <a:lumOff val="95000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -3145,17 +3209,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -3164,17 +3228,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -3183,27 +3246,24 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea3D>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -3211,11 +3271,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -3223,17 +3291,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:seriesLine>
@@ -3242,12 +3310,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -3256,14 +3321,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
+        <a:prstDash val="sysDash"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -3272,10 +3337,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
@@ -3284,7 +3346,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -3305,10 +3367,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
@@ -3317,14 +3376,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -4473,12 +4526,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>153864</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>102578</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3240000" cy="1750541"/>
+    <xdr:ext cx="3971193" cy="1823810"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -4507,9 +4560,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>751703</xdr:colOff>
+      <xdr:colOff>550571</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>113270</xdr:rowOff>
+      <xdr:rowOff>162691</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3346622" cy="1853513"/>
     <xdr:graphicFrame macro="">
@@ -4540,9 +4593,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>123569</xdr:colOff>
+      <xdr:colOff>7199</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>154460</xdr:rowOff>
+      <xdr:rowOff>153167</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3048000" cy="1771135"/>
     <xdr:graphicFrame macro="">
@@ -55985,202 +56038,215 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
     </row>
     <row r="2" spans="2:14" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
     </row>
     <row r="4" spans="2:14" ht="13.8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:14" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="4"/>
+      <c r="C5" s="8"/>
     </row>
     <row r="6" spans="2:14" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="E6" s="6" t="s">
+      <c r="C6" s="8"/>
+      <c r="E6" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="8" t="s">
+      <c r="F6" s="30"/>
+      <c r="G6" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="10" t="s">
+      <c r="H6" s="34"/>
+      <c r="I6" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="J6" s="11"/>
-      <c r="K6" s="12" t="s">
+      <c r="J6" s="38"/>
+      <c r="K6" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="L6" s="13"/>
+      <c r="L6" s="42"/>
     </row>
     <row r="7" spans="2:14" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E7" s="14"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="21"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="44"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="E8" s="22">
+      <c r="C8" s="8"/>
+      <c r="E8" s="12">
         <f>SUMIFS([1]Calc!$F$2:$F$2991,[1]Calc!$J$2:$J$2991,1)</f>
         <v>9197812.7799999844</v>
       </c>
-      <c r="F8" s="23"/>
-      <c r="G8" s="24">
+      <c r="F8" s="13"/>
+      <c r="G8" s="16">
         <f>SUMIFS([1]Calc!$G$2:$G$2991,[1]Calc!$J$2:$J$2991,1)</f>
         <v>1793377.2699999991</v>
       </c>
-      <c r="H8" s="25"/>
-      <c r="I8" s="26">
+      <c r="H8" s="17"/>
+      <c r="I8" s="20">
         <f>SUMIFS([1]Calc!$E$2:$E$2991,[1]Calc!$J$2:$J$2991,1)</f>
         <v>6078</v>
       </c>
-      <c r="J8" s="27"/>
-      <c r="K8" s="28">
+      <c r="J8" s="21"/>
+      <c r="K8" s="24">
         <f>SUMIFS([1]Calc!$K$2:$K$2991,[1]Calc!$J$2:$J$2991,1)</f>
         <v>2985</v>
       </c>
-      <c r="L8" s="29"/>
+      <c r="L8" s="25"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="35"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="37"/>
+      <c r="C9" s="8"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="27"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="4"/>
+      <c r="C11" s="8"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="4"/>
+      <c r="C12" s="8"/>
     </row>
     <row r="14" spans="2:14" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="38" t="s">
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="38" t="s">
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
     </row>
     <row r="27" spans="2:14" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="B27" s="38" t="s">
+      <c r="B27" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="38" t="s">
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B41" s="39" t="s">
+      <c r="B41" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C41" s="40"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="40"/>
-      <c r="F41" s="40"/>
-      <c r="G41" s="40"/>
-      <c r="H41" s="40"/>
-      <c r="I41" s="40"/>
-      <c r="J41" s="40"/>
-      <c r="K41" s="40"/>
-      <c r="L41" s="40"/>
-      <c r="M41" s="40"/>
-      <c r="N41" s="41"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="3"/>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B42" s="42"/>
-      <c r="C42" s="43"/>
-      <c r="D42" s="43"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
-      <c r="J42" s="43"/>
-      <c r="K42" s="43"/>
-      <c r="L42" s="43"/>
-      <c r="M42" s="43"/>
-      <c r="N42" s="44"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B1:N2"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="E6:F7"/>
+    <mergeCell ref="G6:H7"/>
+    <mergeCell ref="I6:J7"/>
+    <mergeCell ref="K6:L7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
+    <mergeCell ref="I8:J9"/>
+    <mergeCell ref="K8:L9"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="B41:N42"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
@@ -56189,22 +56255,9 @@
     <mergeCell ref="K14:N14"/>
     <mergeCell ref="B27:G27"/>
     <mergeCell ref="H27:N27"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
-    <mergeCell ref="I8:J9"/>
-    <mergeCell ref="K8:L9"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B1:N2"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="E6:F7"/>
-    <mergeCell ref="G6:H7"/>
-    <mergeCell ref="I6:J7"/>
-    <mergeCell ref="K6:L7"/>
   </mergeCells>
   <pageMargins left="0.15" right="0.15" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>